--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,791 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128842488</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>477149</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6851177</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128842595</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6851190</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128842110</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80222</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477087</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6851161</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128842304</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57820</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477124</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851169</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128841906</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477105</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6851128</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128842141</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6851166</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128842371</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477114</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6851164</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128842567</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79148</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477117</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6851203</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -980,48 +980,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>57827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R5" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,57 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>57827</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R6" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,57 +980,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>57827</v>
+        <v>80141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R5" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,48 +1077,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>57827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R6" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129070552</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129070177</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129070552</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129070177</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -980,48 +980,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B5" t="n">
-        <v>80145</v>
+        <v>57829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R5" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,57 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>57829</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R6" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,57 +980,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>57829</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R5" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,48 +1077,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R6" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129070552</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129070177</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -980,48 +980,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>57831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R5" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,57 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R6" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -980,57 +980,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B5" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R5" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,48 +1077,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B6" t="n">
-        <v>80147</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R6" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -980,48 +980,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842110</v>
+        <v>128842304</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>57831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477087</v>
+        <v>477124</v>
       </c>
       <c r="R5" t="n">
-        <v>6851161</v>
+        <v>6851169</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,57 +1086,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842304</v>
+        <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477124</v>
+        <v>477087</v>
       </c>
       <c r="R6" t="n">
-        <v>6851169</v>
+        <v>6851161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128842595</v>
       </c>
       <c r="B4" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128841906</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>128842567</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129070552</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129070177</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>129070552</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129070177</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>129070421</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149748</v>
+        <v>128841906</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477212</v>
+        <v>477105</v>
       </c>
       <c r="R2" t="n">
-        <v>6851096</v>
+        <v>6851128</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +775,7 @@
         <v>128842488</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128842595</v>
+        <v>128842567</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477100</v>
+        <v>477117</v>
       </c>
       <c r="R4" t="n">
-        <v>6851190</v>
+        <v>6851203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128842304</v>
+        <v>128842595</v>
       </c>
       <c r="B5" t="n">
-        <v>57831</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477124</v>
+        <v>477100</v>
       </c>
       <c r="R5" t="n">
-        <v>6851169</v>
+        <v>6851190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1066,7 @@
         <v>128842110</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128841906</v>
+        <v>121149748</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1171,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blästermyran, Blästermyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477105</v>
+        <v>477212</v>
       </c>
       <c r="R7" t="n">
-        <v>6851128</v>
+        <v>6851096</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,12 +1229,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,12 +1254,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1283,7 +1269,7 @@
         <v>128842141</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1366,7 @@
         <v>128842371</v>
       </c>
       <c r="B9" t="n">
-        <v>80148</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128842567</v>
+        <v>129070177</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1485,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1509,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477117</v>
+        <v>477225</v>
       </c>
       <c r="R10" t="n">
-        <v>6851203</v>
+        <v>6851095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,12 +1525,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,66 +1545,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129070421</v>
+        <v>129070552</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477222</v>
+        <v>477149</v>
       </c>
       <c r="R11" t="n">
-        <v>6851003</v>
+        <v>6851019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129070552</v>
+        <v>128842304</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>58057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,34 +1665,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477149</v>
+        <v>477124</v>
       </c>
       <c r="R12" t="n">
-        <v>6851019</v>
+        <v>6851169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,12 +1728,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,57 +1748,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129070177</v>
+        <v>129070421</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477225</v>
+        <v>477222</v>
       </c>
       <c r="R13" t="n">
-        <v>6851095</v>
+        <v>6851003</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,7 +1869,7 @@
         <v>129073775</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128841906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842567</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149748</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842371</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070177</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842304</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070421</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,8 +2025,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129073775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44202-2025 artfynd.xlsx
+++ b/artfynd/A 44202-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128842110</v>
+        <v>135913282</v>
       </c>
       <c r="B6" t="n">
-        <v>80433</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477087</v>
+        <v>477202</v>
       </c>
       <c r="R6" t="n">
-        <v>6851161</v>
+        <v>6851008</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1173,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128842110</t>
+          <t>https://artportalen.se/Sighting/135913282</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121149748</v>
+        <v>135912990</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,38 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477212</v>
+        <v>477236</v>
       </c>
       <c r="R7" t="n">
-        <v>6851096</v>
+        <v>6851031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1259,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,27 +1275,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121149748</t>
+          <t>https://artportalen.se/Sighting/135912990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128842141</v>
+        <v>128842110</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477109</v>
+        <v>477087</v>
       </c>
       <c r="R8" t="n">
-        <v>6851166</v>
+        <v>6851161</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1397,16 +1388,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128842141</t>
+          <t>https://artportalen.se/Sighting/128842110</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128842371</v>
+        <v>135913659</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,37 +1405,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477114</v>
+        <v>477192</v>
       </c>
       <c r="R9" t="n">
-        <v>6851164</v>
+        <v>6850996</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,27 +1488,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128842371</t>
+          <t>https://artportalen.se/Sighting/135913659</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129070177</v>
+        <v>135913639</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>93359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477225</v>
+        <v>477171</v>
       </c>
       <c r="R10" t="n">
-        <v>6851095</v>
+        <v>6850979</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,16 +1601,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070177</t>
+          <t>https://artportalen.se/Sighting/135913639</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129070552</v>
+        <v>135913728</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477149</v>
+        <v>477180</v>
       </c>
       <c r="R11" t="n">
-        <v>6851019</v>
+        <v>6851015</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1703,16 +1703,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070552</t>
+          <t>https://artportalen.se/Sighting/135913728</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128842304</v>
+        <v>135913375</v>
       </c>
       <c r="B12" t="n">
-        <v>58057</v>
+        <v>80060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,46 +1720,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477124</v>
+        <v>477198</v>
       </c>
       <c r="R12" t="n">
-        <v>6851169</v>
+        <v>6851020</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,74 +1794,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128842304</t>
+          <t>https://artportalen.se/Sighting/135913375</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129070421</v>
+        <v>121149748</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Blästermyran, Blästermyran, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477222</v>
+        <v>477212</v>
       </c>
       <c r="R13" t="n">
-        <v>6851003</v>
+        <v>6851096</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,12 +1880,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,49 +1905,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070421</t>
+          <t>https://artportalen.se/Sighting/121149748</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129073775</v>
+        <v>128842141</v>
       </c>
       <c r="B14" t="n">
-        <v>97983</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1966,13 +1957,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477202</v>
+        <v>477109</v>
       </c>
       <c r="R14" t="n">
-        <v>6851142</v>
+        <v>6851166</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1996,12 +1987,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,16 +2007,1786 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842141</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128842371</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477114</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6851164</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842371</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129070177</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477225</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6851095</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070177</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129070552</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477149</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6851019</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070552</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135913386</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477196</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6851057</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913386</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135913572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477188</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6850983</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913572</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135913780</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477161</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6851028</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913780</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135913668</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>477166</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6850974</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913668</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128842304</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477124</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6851169</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842304</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129070421</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>477222</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6851003</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070421</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135912913</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>477229</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6851030</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135912913</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135913234</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>477210</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6850978</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913234</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135913271</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>477193</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6850994</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913271</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135913325</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477202</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6851010</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913325</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135913337</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477211</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6851010</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913337</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135913491</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>477178</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6850994</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913491</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135917516</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>477179</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6851089</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917516</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129073775</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Blästermyran, Blästermyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>477202</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6851142</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129073775</t>
         </is>
@@ -2046,6 +3807,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
